--- a/MoTaCongViec.xlsx
+++ b/MoTaCongViec.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="13420"/>
+    <workbookView windowWidth="28260" windowHeight="13400"/>
   </bookViews>
   <sheets>
     <sheet name="Mô tả công việc" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="33">
   <si>
     <t>STT</t>
   </si>
@@ -99,6 +99,12 @@
     <t>1. Nộp mô tả usecase
 2. Coding, Đưa source lên GIT, gửi link github
 3. Nộp phân công công việc nhóm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Tiến hành rà soát, chỉnh sửa và hoàn thiện mô hình ERD (Entity-Relationship Diagram) để đảm bảo phản ánh chính xác các mối quan hệ nghiệp vụ trong hệ thống. Cập nhật các bảng, khóa chính, khóa ngoại, cũng như các ràng buộc dữ liệu để mô hình dữ liệu vừa tối ưu vừa linh hoạt cho việc triển khai ứng dụng. Đồng thời, thiết kế cơ sở dữ liệu thực tế dựa trên ERD đã chỉnh sửa, đảm bảo tính toàn vẹn dữ liệu, khả năng mở rộng, cũng như đáp ứng đầy đủ các nghiệp vụ của hệ thống quản lý sự kiện.
+2.  Tiếp tục phát triển giao diện và chức năng (giao diện của trang tổ chức và quản trị viên với các chức năng thêm xóa sửa để có thể coi, tạo sự kiện và duyệt sự kiện).
+3. Tiếp tục thực hiện việc viết và hoàn thiện phần mô tả chi tiết về quy trình triển khai hệ thống, thiết kế cơ sở dữ liệu, kiến trúc phần mềm và các chức năng của ứng dụng.
+</t>
   </si>
   <si>
     <t>16/11/2025</t>
@@ -793,7 +799,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -815,9 +821,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1170,7 +1173,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1212,30 +1215,32 @@
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="51" spans="1:5">
+    <row r="5" ht="269" spans="1:5">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="E5" s="7" t="s">
         <v>8</v>
       </c>
@@ -1245,10 +1250,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
@@ -1260,10 +1265,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>19</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7" t="s">
@@ -1275,10 +1280,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7" t="s">
@@ -1289,11 +1294,11 @@
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>22</v>
+      <c r="B9" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="s">
@@ -1305,10 +1310,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>23</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7" t="s">
@@ -1319,11 +1324,11 @@
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>25</v>
+      <c r="B11" s="10" t="s">
+        <v>26</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7" t="s">
@@ -1334,11 +1339,11 @@
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>26</v>
+      <c r="B12" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
@@ -1349,11 +1354,11 @@
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>27</v>
+      <c r="B13" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
@@ -1364,11 +1369,11 @@
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>28</v>
+      <c r="B14" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
@@ -1379,11 +1384,11 @@
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>29</v>
+      <c r="B15" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
@@ -1394,11 +1399,11 @@
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>30</v>
+      <c r="B16" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7" t="s">

--- a/MoTaCongViec.xlsx
+++ b/MoTaCongViec.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="13400"/>
+    <workbookView windowWidth="28260" windowHeight="13420"/>
   </bookViews>
   <sheets>
     <sheet name="Mô tả công việc" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1415,4 +1416,15 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/MoTaCongViec.xlsx
+++ b/MoTaCongViec.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="13420"/>
+    <workbookView windowWidth="29400" windowHeight="13420"/>
   </bookViews>
   <sheets>
     <sheet name="Mô tả công việc" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="35">
   <si>
     <t>STT</t>
   </si>
@@ -116,7 +116,16 @@
 3. Nộp phân công công việc nhóm</t>
   </si>
   <si>
+    <t>Báo cáo trên trường</t>
+  </si>
+  <si>
     <t>23/11/2025</t>
+  </si>
+  <si>
+    <t>1. Chỉnh sửa lại sơ đồ tuần tự cho phù hợp với mô hình MVC do giảng viên hướng dẫn. 
+2. TIếp tục phát triển ứng dụng theo model chức năng.
+3. Thêm các validate cho các chức năng của model đăng ký đăng nhập, quản lý sự kiện, quản lý loại vé và quản lý suất diễn.
+4. Chức năng đặt vé và thành toán.</t>
   </si>
   <si>
     <t>30/11/2025</t>
@@ -800,7 +809,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -822,6 +831,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1174,7 +1186,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1216,7 +1228,7 @@
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="9" t="s">
@@ -1233,7 +1245,7 @@
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="9" t="s">
@@ -1256,22 +1268,26 @@
       <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="7"/>
+      <c r="D6" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="51" spans="1:5">
+    <row r="7" ht="101" spans="1:5">
       <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="10" t="s">
+        <v>23</v>
+      </c>
       <c r="E7" s="7" t="s">
         <v>8</v>
       </c>
@@ -1281,7 +1297,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>20</v>
@@ -1295,11 +1311,11 @@
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>23</v>
+      <c r="B9" s="14" t="s">
+        <v>25</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7" t="s">
@@ -1311,10 +1327,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7" t="s">
@@ -1325,11 +1341,11 @@
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>26</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>24</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7" t="s">
@@ -1340,11 +1356,11 @@
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>27</v>
+      <c r="B12" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7" t="s">
@@ -1355,11 +1371,11 @@
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>28</v>
+      <c r="B13" s="15" t="s">
+        <v>30</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7" t="s">
@@ -1370,11 +1386,11 @@
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>29</v>
+      <c r="B14" s="13" t="s">
+        <v>31</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="7" t="s">
@@ -1385,11 +1401,11 @@
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>30</v>
+      <c r="B15" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7" t="s">
@@ -1400,11 +1416,11 @@
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>31</v>
+      <c r="B16" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7" t="s">

--- a/MoTaCongViec.xlsx
+++ b/MoTaCongViec.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="13420"/>
+    <workbookView windowWidth="29400" windowHeight="13400"/>
   </bookViews>
   <sheets>
     <sheet name="Mô tả công việc" sheetId="1" r:id="rId1"/>
@@ -809,7 +809,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -831,9 +831,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1186,7 +1183,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1228,7 +1225,7 @@
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="9" t="s">
@@ -1245,7 +1242,7 @@
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="9" t="s">
@@ -1285,7 +1282,7 @@
       <c r="C7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E7" s="7" t="s">
@@ -1311,7 +1308,7 @@
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="9" t="s">
@@ -1341,7 +1338,7 @@
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="9" t="s">
@@ -1356,7 +1353,7 @@
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="9" t="s">
@@ -1371,7 +1368,7 @@
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>30</v>
       </c>
       <c r="C13" s="9" t="s">
@@ -1386,7 +1383,7 @@
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="12" t="s">
         <v>31</v>
       </c>
       <c r="C14" s="9" t="s">
@@ -1401,7 +1398,7 @@
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C15" s="9" t="s">
@@ -1416,7 +1413,7 @@
       <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>33</v>
       </c>
       <c r="C16" s="7" t="s">
